--- a/nr-update-missing-fields/ig/StructureDefinition-as-ext-data-trace.xlsx
+++ b/nr-update-missing-fields/ig/StructureDefinition-as-ext-data-trace.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T07:52:36+00:00</t>
+    <t>2024-07-17T09:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-missing-fields/ig/StructureDefinition-as-ext-data-trace.xlsx
+++ b/nr-update-missing-fields/ig/StructureDefinition-as-ext-data-trace.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="145">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T09:13:15+00:00</t>
+    <t>2024-07-17T12:12:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Extension créée dans le cadre de l'Annuaire Santé pour tracer l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI)). Des études complémentaires vont être initiées pour envisager l'usage de la ressource Provenance ou meta.source</t>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour tracer l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI)). Des études complémentaires vont être initiées pour envisager l'usage de la ressource Provenance ou meta.source.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -432,6 +432,31 @@
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/as-vs-type-systeme-information</t>
+  </si>
+  <si>
+    <t>Extension.extension:date-maj-ae</t>
+  </si>
+  <si>
+    <t>date-maj-ae</t>
+  </si>
+  <si>
+    <t>Date de mise à jour de la ressource de l'autorité d'enregistrement. Cette date est différente de l'atttribut lastUpdated dû au délai entre la mise à jour de la donnée au niveau de l'autorité d'enregistrement et la publication de la ressource technique au niveau de l'API FHIR.</t>
+  </si>
+  <si>
+    <t>Extension.extension:date-maj-ae.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:date-maj-ae.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:date-maj-ae.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:date-maj-ae.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">date
+</t>
   </si>
   <si>
     <t>base64Binary
@@ -745,7 +770,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK16"/>
+  <dimension ref="A1:AK21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="51.859375" customWidth="true" bestFit="true"/>
@@ -2246,18 +2271,20 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="C15" s="2"/>
+        <v>90</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="D15" t="s" s="2">
         <v>76</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>84</v>
@@ -2272,24 +2299,22 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" t="s" s="2">
-        <v>3</v>
+        <v>76</v>
       </c>
       <c r="S15" t="s" s="2">
         <v>76</v>
@@ -2331,30 +2356,30 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>100</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2365,7 +2390,7 @@
         <v>77</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>76</v>
@@ -2377,13 +2402,13 @@
         <v>76</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>119</v>
+        <v>86</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2434,21 +2459,540 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK16" t="s" s="2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K17" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q17" s="2"/>
+      <c r="R17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K18" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O18" s="2"/>
+      <c r="P18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q18" s="2"/>
+      <c r="R18" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="S18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF18" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK18" t="s" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E19" s="2"/>
+      <c r="F19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K19" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q19" s="2"/>
+      <c r="R19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF19" t="s" s="2">
         <v>123</v>
       </c>
-      <c r="AG16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI16" t="s" s="2">
+      <c r="AG19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI19" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AJ16" t="s" s="2">
+      <c r="AJ19" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="AK16" t="s" s="2">
+      <c r="AK19" t="s" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K20" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O20" s="2"/>
+      <c r="P20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q20" s="2"/>
+      <c r="R20" t="s" s="2">
+        <v>3</v>
+      </c>
+      <c r="S20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q21" s="2"/>
+      <c r="R21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AK21" t="s" s="2">
         <v>100</v>
       </c>
     </row>

--- a/nr-update-missing-fields/ig/StructureDefinition-as-ext-data-trace.xlsx
+++ b/nr-update-missing-fields/ig/StructureDefinition-as-ext-data-trace.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T12:12:47+00:00</t>
+    <t>2024-07-17T15:12:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-missing-fields/ig/StructureDefinition-as-ext-data-trace.xlsx
+++ b/nr-update-missing-fields/ig/StructureDefinition-as-ext-data-trace.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T15:12:21+00:00</t>
+    <t>2024-07-25T07:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
